--- a/experiment/ELAN_bestx8/Test/results-B100/B100.xlsx
+++ b/experiment/ELAN_bestx8/Test/results-B100/B100.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21.47</v>
+        <v>22.48</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3589</v>
+        <v>0.4232</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24.9</v>
+        <v>26.58</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6494</v>
+        <v>0.7336</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23.22</v>
+        <v>23.99</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6335</v>
+        <v>0.7113</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26.42</v>
+        <v>27.64</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6424</v>
+        <v>0.7173</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23.4</v>
+        <v>24.07</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5068</v>
+        <v>0.5615</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>28.44</v>
+        <v>30.81</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7481</v>
+        <v>0.8411</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22.12</v>
+        <v>22.95</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4649</v>
+        <v>0.5353</v>
       </c>
     </row>
     <row r="9">
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21.01</v>
+        <v>21.31</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3663</v>
+        <v>0.4055</v>
       </c>
     </row>
     <row r="10">
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23.26</v>
+        <v>24.14</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.6365</v>
       </c>
     </row>
     <row r="11">
@@ -569,10 +569,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>25.79</v>
+        <v>26.57</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6098</v>
+        <v>0.6745</v>
       </c>
     </row>
     <row r="12">
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19.78</v>
+        <v>21.8</v>
       </c>
       <c r="C12" t="n">
-        <v>0.423</v>
+        <v>0.5536</v>
       </c>
     </row>
     <row r="13">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>23.5</v>
+        <v>24.18</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4479</v>
+        <v>0.5202</v>
       </c>
     </row>
     <row r="14">
@@ -608,10 +608,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>25.9</v>
+        <v>26.84</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5768</v>
+        <v>0.6461</v>
       </c>
     </row>
     <row r="15">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>24.54</v>
+        <v>26.44</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6448</v>
+        <v>0.7319</v>
       </c>
     </row>
     <row r="16">
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>22.29</v>
+        <v>23</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4666</v>
+        <v>0.5263</v>
       </c>
     </row>
     <row r="17">
@@ -647,10 +647,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>19.69</v>
+        <v>20.73</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4003</v>
+        <v>0.5046</v>
       </c>
     </row>
     <row r="18">
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>29.7</v>
+        <v>31.96</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7435</v>
+        <v>0.8328</v>
       </c>
     </row>
     <row r="19">
@@ -673,10 +673,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>28.97</v>
+        <v>30.69</v>
       </c>
       <c r="C19" t="n">
-        <v>0.749</v>
+        <v>0.8355</v>
       </c>
     </row>
     <row r="20">
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>21.9</v>
+        <v>23.91</v>
       </c>
       <c r="C20" t="n">
-        <v>0.5293</v>
+        <v>0.6379</v>
       </c>
     </row>
     <row r="21">
@@ -699,10 +699,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>22.35</v>
+        <v>23.35</v>
       </c>
       <c r="C21" t="n">
-        <v>0.6248</v>
+        <v>0.7127</v>
       </c>
     </row>
     <row r="22">
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>18.63</v>
+        <v>19.64</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3575</v>
+        <v>0.4718</v>
       </c>
     </row>
     <row r="23">
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>20.39</v>
+        <v>21.25</v>
       </c>
       <c r="C23" t="n">
-        <v>0.3378</v>
+        <v>0.4211</v>
       </c>
     </row>
     <row r="24">
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>22.95</v>
+        <v>23.37</v>
       </c>
       <c r="C24" t="n">
-        <v>0.3983</v>
+        <v>0.4398</v>
       </c>
     </row>
     <row r="25">
@@ -751,10 +751,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>22.74</v>
+        <v>23.97</v>
       </c>
       <c r="C25" t="n">
-        <v>0.5276</v>
+        <v>0.6388</v>
       </c>
     </row>
     <row r="26">
@@ -764,10 +764,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>22.48</v>
+        <v>23.82</v>
       </c>
       <c r="C26" t="n">
-        <v>0.5507</v>
+        <v>0.6503</v>
       </c>
     </row>
     <row r="27">
@@ -777,10 +777,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>22.95</v>
+        <v>23.56</v>
       </c>
       <c r="C27" t="n">
-        <v>0.6357</v>
+        <v>0.7168</v>
       </c>
     </row>
     <row r="28">
@@ -790,10 +790,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>23.99</v>
+        <v>24.9</v>
       </c>
       <c r="C28" t="n">
-        <v>0.529</v>
+        <v>0.5937</v>
       </c>
     </row>
     <row r="29">
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>26.08</v>
+        <v>26.75</v>
       </c>
       <c r="C29" t="n">
-        <v>0.6094000000000001</v>
+        <v>0.671</v>
       </c>
     </row>
     <row r="30">
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>25.34</v>
+        <v>28.32</v>
       </c>
       <c r="C30" t="n">
-        <v>0.7531</v>
+        <v>0.842</v>
       </c>
     </row>
     <row r="31">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>18</v>
+        <v>18.4</v>
       </c>
       <c r="C31" t="n">
-        <v>0.3061</v>
+        <v>0.3554</v>
       </c>
     </row>
     <row r="32">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>25.78</v>
+        <v>26.52</v>
       </c>
       <c r="C32" t="n">
-        <v>0.5848</v>
+        <v>0.6488</v>
       </c>
     </row>
     <row r="33">
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>19.41</v>
+        <v>19.62</v>
       </c>
       <c r="C33" t="n">
-        <v>0.2032</v>
+        <v>0.2312</v>
       </c>
     </row>
     <row r="34">
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>21.56</v>
+        <v>22.17</v>
       </c>
       <c r="C34" t="n">
-        <v>0.3546</v>
+        <v>0.4146</v>
       </c>
     </row>
     <row r="35">
@@ -881,10 +881,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>21.25</v>
+        <v>22.17</v>
       </c>
       <c r="C35" t="n">
-        <v>0.5266999999999999</v>
+        <v>0.627</v>
       </c>
     </row>
     <row r="36">
@@ -894,10 +894,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>27.11</v>
+        <v>31.55</v>
       </c>
       <c r="C36" t="n">
-        <v>0.7165</v>
+        <v>0.8358</v>
       </c>
     </row>
     <row r="37">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>22.84</v>
+        <v>23.82</v>
       </c>
       <c r="C37" t="n">
-        <v>0.517</v>
+        <v>0.5964</v>
       </c>
     </row>
     <row r="38">
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>26.32</v>
+        <v>27</v>
       </c>
       <c r="C38" t="n">
-        <v>0.4142</v>
+        <v>0.4478</v>
       </c>
     </row>
     <row r="39">
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>24.81</v>
+        <v>26.11</v>
       </c>
       <c r="C39" t="n">
-        <v>0.5416</v>
+        <v>0.6212</v>
       </c>
     </row>
     <row r="40">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>24.86</v>
+        <v>25.95</v>
       </c>
       <c r="C40" t="n">
-        <v>0.5119</v>
+        <v>0.5803</v>
       </c>
     </row>
     <row r="41">
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>25.21</v>
+        <v>29.03</v>
       </c>
       <c r="C41" t="n">
-        <v>0.6745</v>
+        <v>0.8375</v>
       </c>
     </row>
     <row r="42">
@@ -972,10 +972,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>22.43</v>
+        <v>23.95</v>
       </c>
       <c r="C42" t="n">
-        <v>0.5203</v>
+        <v>0.6131</v>
       </c>
     </row>
     <row r="43">
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>22.2</v>
+        <v>23.34</v>
       </c>
       <c r="C43" t="n">
-        <v>0.4958</v>
+        <v>0.5849</v>
       </c>
     </row>
     <row r="44">
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>23.26</v>
+        <v>24.09</v>
       </c>
       <c r="C44" t="n">
-        <v>0.5802</v>
+        <v>0.6576</v>
       </c>
     </row>
     <row r="45">
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>21.72</v>
+        <v>23.49</v>
       </c>
       <c r="C45" t="n">
-        <v>0.6008</v>
+        <v>0.7186</v>
       </c>
     </row>
     <row r="46">
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>22.25</v>
+        <v>22.71</v>
       </c>
       <c r="C46" t="n">
-        <v>0.4338</v>
+        <v>0.5014999999999999</v>
       </c>
     </row>
     <row r="47">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>30.3</v>
+        <v>32.47</v>
       </c>
       <c r="C47" t="n">
-        <v>0.7272999999999999</v>
+        <v>0.8157</v>
       </c>
     </row>
     <row r="48">
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>19.6</v>
+        <v>20.21</v>
       </c>
       <c r="C48" t="n">
-        <v>0.3438</v>
+        <v>0.4085</v>
       </c>
     </row>
     <row r="49">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>22.34</v>
+        <v>22.78</v>
       </c>
       <c r="C49" t="n">
-        <v>0.3755</v>
+        <v>0.4243</v>
       </c>
     </row>
     <row r="50">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>20.13</v>
+        <v>22.19</v>
       </c>
       <c r="C50" t="n">
-        <v>0.5488</v>
+        <v>0.6934</v>
       </c>
     </row>
     <row r="51">
@@ -1089,10 +1089,10 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>28.52</v>
+        <v>30.1</v>
       </c>
       <c r="C51" t="n">
-        <v>0.7029</v>
+        <v>0.7814</v>
       </c>
     </row>
     <row r="52">
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>22.38</v>
+        <v>22.96</v>
       </c>
       <c r="C52" t="n">
-        <v>0.4215</v>
+        <v>0.4781</v>
       </c>
     </row>
     <row r="53">
@@ -1115,10 +1115,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>19.4</v>
+        <v>19.88</v>
       </c>
       <c r="C53" t="n">
-        <v>0.471</v>
+        <v>0.537</v>
       </c>
     </row>
     <row r="54">
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>28.71</v>
+        <v>29.59</v>
       </c>
       <c r="C54" t="n">
-        <v>0.7004</v>
+        <v>0.769</v>
       </c>
     </row>
     <row r="55">
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>29.58</v>
+        <v>30.63</v>
       </c>
       <c r="C55" t="n">
-        <v>0.6454</v>
+        <v>0.7212</v>
       </c>
     </row>
     <row r="56">
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>23.06</v>
+        <v>24.41</v>
       </c>
       <c r="C56" t="n">
-        <v>0.5029</v>
+        <v>0.6078</v>
       </c>
     </row>
     <row r="57">
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>21.47</v>
+        <v>22.71</v>
       </c>
       <c r="C57" t="n">
-        <v>0.4311</v>
+        <v>0.5159</v>
       </c>
     </row>
     <row r="58">
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>19.83</v>
+        <v>20.13</v>
       </c>
       <c r="C58" t="n">
-        <v>0.2261</v>
+        <v>0.2602</v>
       </c>
     </row>
     <row r="59">
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>25.04</v>
+        <v>25.61</v>
       </c>
       <c r="C59" t="n">
-        <v>0.55</v>
+        <v>0.6177</v>
       </c>
     </row>
     <row r="60">
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>29.45</v>
+        <v>30.28</v>
       </c>
       <c r="C60" t="n">
-        <v>0.6581</v>
+        <v>0.724</v>
       </c>
     </row>
     <row r="61">
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>27.22</v>
+        <v>29.3</v>
       </c>
       <c r="C61" t="n">
-        <v>0.6274999999999999</v>
+        <v>0.7201</v>
       </c>
     </row>
     <row r="62">
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>28.7</v>
+        <v>29.7</v>
       </c>
       <c r="C62" t="n">
-        <v>0.6695</v>
+        <v>0.7454</v>
       </c>
     </row>
     <row r="63">
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>25.22</v>
+        <v>26.5</v>
       </c>
       <c r="C63" t="n">
-        <v>0.6367</v>
+        <v>0.7088</v>
       </c>
     </row>
     <row r="64">
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>21.74</v>
+        <v>24.04</v>
       </c>
       <c r="C64" t="n">
-        <v>0.7219</v>
+        <v>0.8611</v>
       </c>
     </row>
     <row r="65">
@@ -1271,10 +1271,10 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>21.34</v>
+        <v>21.72</v>
       </c>
       <c r="C65" t="n">
-        <v>0.3859</v>
+        <v>0.4337</v>
       </c>
     </row>
     <row r="66">
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>22.41</v>
+        <v>23.68</v>
       </c>
       <c r="C66" t="n">
-        <v>0.3966</v>
+        <v>0.4622</v>
       </c>
     </row>
     <row r="67">
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>24.19</v>
+        <v>25.54</v>
       </c>
       <c r="C67" t="n">
-        <v>0.5982</v>
+        <v>0.6711</v>
       </c>
     </row>
     <row r="68">
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>31.04</v>
+        <v>35.01</v>
       </c>
       <c r="C68" t="n">
-        <v>0.8555</v>
+        <v>0.9613</v>
       </c>
     </row>
     <row r="69">
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>17.88</v>
+        <v>18.46</v>
       </c>
       <c r="C69" t="n">
-        <v>0.2702</v>
+        <v>0.3261</v>
       </c>
     </row>
     <row r="70">
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>20.41</v>
+        <v>21.01</v>
       </c>
       <c r="C70" t="n">
-        <v>0.462</v>
+        <v>0.5165999999999999</v>
       </c>
     </row>
     <row r="71">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>23.32</v>
+        <v>25.17</v>
       </c>
       <c r="C71" t="n">
-        <v>0.5803</v>
+        <v>0.6778</v>
       </c>
     </row>
     <row r="72">
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>25.98</v>
+        <v>27.58</v>
       </c>
       <c r="C72" t="n">
-        <v>0.6303</v>
+        <v>0.7299</v>
       </c>
     </row>
     <row r="73">
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>22.65</v>
+        <v>23.35</v>
       </c>
       <c r="C73" t="n">
-        <v>0.365</v>
+        <v>0.4162</v>
       </c>
     </row>
     <row r="74">
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>24.96</v>
+        <v>25.38</v>
       </c>
       <c r="C74" t="n">
-        <v>0.4221</v>
+        <v>0.4558</v>
       </c>
     </row>
     <row r="75">
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>23.22</v>
+        <v>24.13</v>
       </c>
       <c r="C75" t="n">
-        <v>0.5014</v>
+        <v>0.5765</v>
       </c>
     </row>
     <row r="76">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>20.6</v>
+        <v>21.95</v>
       </c>
       <c r="C76" t="n">
-        <v>0.4785</v>
+        <v>0.5725</v>
       </c>
     </row>
     <row r="77">
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>26.87</v>
+        <v>28.3</v>
       </c>
       <c r="C77" t="n">
-        <v>0.616</v>
+        <v>0.6850000000000001</v>
       </c>
     </row>
     <row r="78">
@@ -1440,10 +1440,10 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>22.11</v>
+        <v>22.55</v>
       </c>
       <c r="C78" t="n">
-        <v>0.2925</v>
+        <v>0.3304</v>
       </c>
     </row>
     <row r="79">
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>25.35</v>
+        <v>26.78</v>
       </c>
       <c r="C79" t="n">
-        <v>0.6076</v>
+        <v>0.6851</v>
       </c>
     </row>
     <row r="80">
@@ -1466,10 +1466,10 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>23.7</v>
+        <v>27.81</v>
       </c>
       <c r="C80" t="n">
-        <v>0.7252999999999999</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="81">
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>27.6</v>
+        <v>28.31</v>
       </c>
       <c r="C81" t="n">
-        <v>0.6795</v>
+        <v>0.7452</v>
       </c>
     </row>
     <row r="82">
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>29.94</v>
+        <v>32.08</v>
       </c>
       <c r="C82" t="n">
-        <v>0.8151</v>
+        <v>0.901</v>
       </c>
     </row>
     <row r="83">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>26.15</v>
+        <v>26.98</v>
       </c>
       <c r="C83" t="n">
-        <v>0.5688</v>
+        <v>0.6328</v>
       </c>
     </row>
     <row r="84">
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>20.17</v>
+        <v>20.65</v>
       </c>
       <c r="C84" t="n">
-        <v>0.3046</v>
+        <v>0.3513</v>
       </c>
     </row>
     <row r="85">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>19.42</v>
+        <v>19.7</v>
       </c>
       <c r="C85" t="n">
-        <v>0.4024</v>
+        <v>0.4603</v>
       </c>
     </row>
     <row r="86">
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>21.34</v>
+        <v>22.91</v>
       </c>
       <c r="C86" t="n">
-        <v>0.5528</v>
+        <v>0.6577</v>
       </c>
     </row>
     <row r="87">
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>22.11</v>
+        <v>22.97</v>
       </c>
       <c r="C87" t="n">
-        <v>0.3544</v>
+        <v>0.4104</v>
       </c>
     </row>
     <row r="88">
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>24.44</v>
+        <v>25.51</v>
       </c>
       <c r="C88" t="n">
-        <v>0.4859</v>
+        <v>0.5597</v>
       </c>
     </row>
     <row r="89">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>25.74</v>
+        <v>27.31</v>
       </c>
       <c r="C89" t="n">
-        <v>0.5847</v>
+        <v>0.6694</v>
       </c>
     </row>
     <row r="90">
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>24.94</v>
+        <v>25.65</v>
       </c>
       <c r="C90" t="n">
-        <v>0.3885</v>
+        <v>0.4306</v>
       </c>
     </row>
     <row r="91">
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>22.45</v>
+        <v>22.72</v>
       </c>
       <c r="C91" t="n">
-        <v>0.3653</v>
+        <v>0.4038</v>
       </c>
     </row>
     <row r="92">
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>25.9</v>
+        <v>26.59</v>
       </c>
       <c r="C92" t="n">
-        <v>0.5182</v>
+        <v>0.5692</v>
       </c>
     </row>
     <row r="93">
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>22.36</v>
+        <v>23.96</v>
       </c>
       <c r="C93" t="n">
-        <v>0.5054</v>
+        <v>0.6109</v>
       </c>
     </row>
     <row r="94">
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>25.43</v>
+        <v>25.98</v>
       </c>
       <c r="C94" t="n">
-        <v>0.6364</v>
+        <v>0.7004</v>
       </c>
     </row>
     <row r="95">
@@ -1661,10 +1661,10 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>21.7</v>
+        <v>23</v>
       </c>
       <c r="C95" t="n">
-        <v>0.4318</v>
+        <v>0.5205</v>
       </c>
     </row>
     <row r="96">
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>21.86</v>
+        <v>22.7</v>
       </c>
       <c r="C96" t="n">
-        <v>0.5282</v>
+        <v>0.617</v>
       </c>
     </row>
     <row r="97">
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>21.12</v>
+        <v>21.29</v>
       </c>
       <c r="C97" t="n">
-        <v>0.1857</v>
+        <v>0.2051</v>
       </c>
     </row>
     <row r="98">
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>25.35</v>
+        <v>25.7</v>
       </c>
       <c r="C98" t="n">
-        <v>0.4158</v>
+        <v>0.4483</v>
       </c>
     </row>
     <row r="99">
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>22.12</v>
+        <v>23.21</v>
       </c>
       <c r="C99" t="n">
-        <v>0.5177</v>
+        <v>0.5949</v>
       </c>
     </row>
     <row r="100">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>23.06</v>
+        <v>24.39</v>
       </c>
       <c r="C100" t="n">
-        <v>0.4972</v>
+        <v>0.5936</v>
       </c>
     </row>
     <row r="101">
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>20.87</v>
+        <v>22.37</v>
       </c>
       <c r="C101" t="n">
-        <v>0.4503</v>
+        <v>0.5347</v>
       </c>
     </row>
     <row r="102">
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>23.66</v>
+        <v>24.85</v>
       </c>
       <c r="C102" t="n">
-        <v>0.5216</v>
+        <v>0.5987</v>
       </c>
     </row>
   </sheetData>
